--- a/VerveStacks_PHL_grids_kan/vt_vervestacks_PHL_v1.xlsx
+++ b/VerveStacks_PHL_grids_kan/vt_vervestacks_PHL_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_PHL_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F5C5C75-A889-4254-AB53-BF5CCE948FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{00E71DEE-474A-453A-AACA-4B98F6DE1429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E9C03567-D316-41A7-96FF-1ADE8E7E283E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C3AA04EC-E3EB-4240-87DE-9833F857C8E5}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -4562,7 +4562,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE858C69-BFB9-4176-B2AD-ACC99A674B81}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E83957E9-AFE5-4266-B98F-FAF5A8626EFD}">
   <dimension ref="B9:V110"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10842,7 +10842,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{353EE9CE-B0C2-437F-BECB-D1874D2627F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27392AF5-0890-46B8-A673-D1E6DE1C9CAE}">
   <dimension ref="B9:V388"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32678,7 +32678,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA160F81-815C-4580-913B-29C48DECD834}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{932A93D3-6373-4AA0-8005-204C600D318A}">
   <dimension ref="B9:V278"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44288,7 +44288,7 @@
         <v>14</v>
       </c>
       <c r="R207" t="s">
-        <v>360</v>
+        <v>484</v>
       </c>
       <c r="S207" t="s">
         <v>355</v>
@@ -44350,7 +44350,7 @@
         <v>14</v>
       </c>
       <c r="R208" t="s">
-        <v>484</v>
+        <v>360</v>
       </c>
       <c r="S208" t="s">
         <v>355</v>
@@ -44722,7 +44722,7 @@
         <v>14</v>
       </c>
       <c r="R214" t="s">
-        <v>360</v>
+        <v>484</v>
       </c>
       <c r="S214" t="s">
         <v>355</v>
@@ -44784,7 +44784,7 @@
         <v>14</v>
       </c>
       <c r="R215" t="s">
-        <v>484</v>
+        <v>360</v>
       </c>
       <c r="S215" t="s">
         <v>355</v>
@@ -44846,7 +44846,7 @@
         <v>14</v>
       </c>
       <c r="R216" t="s">
-        <v>360</v>
+        <v>484</v>
       </c>
       <c r="S216" t="s">
         <v>355</v>
@@ -44908,7 +44908,7 @@
         <v>14</v>
       </c>
       <c r="R217" t="s">
-        <v>484</v>
+        <v>360</v>
       </c>
       <c r="S217" t="s">
         <v>355</v>
@@ -45156,7 +45156,7 @@
         <v>14</v>
       </c>
       <c r="R221" t="s">
-        <v>360</v>
+        <v>484</v>
       </c>
       <c r="S221" t="s">
         <v>355</v>
@@ -45218,7 +45218,7 @@
         <v>14</v>
       </c>
       <c r="R222" t="s">
-        <v>484</v>
+        <v>360</v>
       </c>
       <c r="S222" t="s">
         <v>355</v>
@@ -47249,7 +47249,7 @@
         <v>33</v>
       </c>
       <c r="M264">
-        <v>0.21773415653673134</v>
+        <v>0.21773415653673131</v>
       </c>
     </row>
     <row r="265" spans="2:13" x14ac:dyDescent="0.45">
@@ -47278,7 +47278,7 @@
         <v>33</v>
       </c>
       <c r="M265">
-        <v>0.21773415653673134</v>
+        <v>0.21773415653673131</v>
       </c>
     </row>
     <row r="266" spans="2:13" x14ac:dyDescent="0.45">
@@ -47307,7 +47307,7 @@
         <v>33</v>
       </c>
       <c r="M266">
-        <v>0.21773415653673134</v>
+        <v>0.21773415653673131</v>
       </c>
     </row>
     <row r="267" spans="2:13" x14ac:dyDescent="0.45">
@@ -47772,7 +47772,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE8319F9-857A-4435-B3C4-3522CB67CC50}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6A330AE-8E18-4506-BC7B-5FC725135A9B}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
